--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: February · solver HiGHS Optimal · run 2026-09-04 09:46 UTC · 27 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 113 ms</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15269148.89</v>
+        <v>11244178.48</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1013.67</v>
+        <v>656.12</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8791</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8791</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6631</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3369</v>
+        <v>0</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2623</v>
+        <v>0.1338</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="46" customWidth="1" min="11" max="11"/>
@@ -851,26 +851,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Port Province</t>
+          <t>National Capital District</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>168000</v>
       </c>
       <c r="E2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="F2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>239423.75</v>
+        <v>214579.72</v>
       </c>
       <c r="I2" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>0.08</v>
       </c>
       <c r="N2" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="O2" t="n">
         <v>0.0262</v>
@@ -935,10 +935,10 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>190307.95</v>
+        <v>170630.63</v>
       </c>
       <c r="I3" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>86725.24000000001</v>
+        <v>77631.94</v>
       </c>
       <c r="I4" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>77112.55</v>
+        <v>69062.73</v>
       </c>
       <c r="I5" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>54638.41</v>
+        <v>48973.73</v>
       </c>
       <c r="I6" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1207,10 +1207,10 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>78991.39</v>
+        <v>68998.74000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1275,19 +1275,19 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>558714.8</v>
+        <v>70724.14999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>13.3</v>
+        <v>1.68</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Port Moresby Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.3032</v>
+        <v>0.08</v>
       </c>
       <c r="N8" t="n">
         <v>50.4</v>
@@ -1343,19 +1343,19 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>252751.93</v>
+        <v>33022.85</v>
       </c>
       <c r="I9" t="n">
-        <v>13.3</v>
+        <v>1.74</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Port Moresby Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.3246</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>40.5</v>
@@ -1411,10 +1411,10 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>70976.08</v>
+        <v>61457.84</v>
       </c>
       <c r="I10" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>149656.94</v>
+        <v>127303.83</v>
       </c>
       <c r="I11" t="n">
-        <v>12.47</v>
+        <v>10.61</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1547,19 +1547,19 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>212843.73</v>
+        <v>25262.18</v>
       </c>
       <c r="I12" t="n">
-        <v>13.3</v>
+        <v>1.58</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Port Moresby Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.4118</v>
+        <v>0.1173</v>
       </c>
       <c r="N12" t="n">
         <v>36</v>
@@ -1615,10 +1615,10 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>128242.68</v>
+        <v>109685.29</v>
       </c>
       <c r="I13" t="n">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>39812.68</v>
+        <v>37084.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1751,10 +1751,10 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>60666.94</v>
+        <v>56510.16</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1819,10 +1819,10 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>34125.15</v>
+        <v>31786.97</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1887,19 +1887,19 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>319265.6</v>
+        <v>46166.45</v>
       </c>
       <c r="I17" t="n">
-        <v>13.3</v>
+        <v>1.92</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Port Moresby Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.4118</v>
+        <v>0.1173</v>
       </c>
       <c r="N17" t="n">
         <v>36</v>
@@ -1955,10 +1955,10 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>144982.45</v>
+        <v>123288.87</v>
       </c>
       <c r="I18" t="n">
-        <v>13.18</v>
+        <v>11.21</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>86621.05</v>
+        <v>81021.58</v>
       </c>
       <c r="I19" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>72199.00999999999</v>
+        <v>69613.55</v>
       </c>
       <c r="I20" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>51835.19</v>
+        <v>49978.96</v>
       </c>
       <c r="I21" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>57388.96</v>
+        <v>55333.85</v>
       </c>
       <c r="I22" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>104130.76</v>
+        <v>97223.64999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>11.57</v>
+        <v>10.8</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2363,10 +2363,10 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>98345.72</v>
+        <v>91822.34</v>
       </c>
       <c r="I24" t="n">
-        <v>11.57</v>
+        <v>10.8</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>13884.43</v>
+        <v>13387.22</v>
       </c>
       <c r="I25" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2499,10 +2499,10 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>115622.99</v>
+        <v>107499.7</v>
       </c>
       <c r="I26" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Losuia Province</t>
+          <t>Milne Bay</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2567,10 +2567,10 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>104634.98</v>
+        <v>102667.02</v>
       </c>
       <c r="I27" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>75770.16</v>
+        <v>74345.08</v>
       </c>
       <c r="I28" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>86594.47</v>
+        <v>84965.81</v>
       </c>
       <c r="I29" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2771,10 +2771,10 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>50513.44</v>
+        <v>49563.39</v>
       </c>
       <c r="I30" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2839,10 +2839,10 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>31703.08</v>
+        <v>29475.73</v>
       </c>
       <c r="I31" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>54121.54</v>
+        <v>53103.63</v>
       </c>
       <c r="I32" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2975,10 +2975,10 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>147701.81</v>
+        <v>137440.59</v>
       </c>
       <c r="I33" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>45766.76</v>
+        <v>42587.22</v>
       </c>
       <c r="I34" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>27043.99</v>
+        <v>25165.18</v>
       </c>
       <c r="I35" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>129013.66</v>
+        <v>109878.54</v>
       </c>
       <c r="I36" t="n">
-        <v>12.9</v>
+        <v>10.99</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3247,10 +3247,10 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>22883.38</v>
+        <v>21293.61</v>
       </c>
       <c r="I37" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3315,10 +3315,10 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>29124.3</v>
+        <v>27100.96</v>
       </c>
       <c r="I38" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3367,26 +3367,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Angau Province</t>
+          <t>Morobe</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>188000</v>
       </c>
       <c r="E39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="F39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>302763.36</v>
+        <v>272844.18</v>
       </c>
       <c r="I39" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>0.08</v>
       </c>
       <c r="N39" t="n">
-        <v>108.3</v>
+        <v>108</v>
       </c>
       <c r="O39" t="n">
         <v>0.0252</v>
@@ -3451,10 +3451,10 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>99880.10000000001</v>
+        <v>89214.67999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3513,22 +3513,37 @@
         <v>108.509</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>108.509</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>53692.33</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1.73</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Lae Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O41" t="n">
         <v>0.275</v>
@@ -3540,7 +3555,7 @@
         <v>4</v>
       </c>
       <c r="R41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3572,10 +3587,10 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>85332.28999999999</v>
+        <v>79188.34</v>
       </c>
       <c r="I42" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3634,22 +3649,37 @@
         <v>126.011</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>126.011</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>68329.67</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1.9</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Lae Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O43" t="n">
         <v>0.3084</v>
@@ -3661,7 +3691,7 @@
         <v>4</v>
       </c>
       <c r="R43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -3693,10 +3723,10 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>236147.68</v>
+        <v>201176.49</v>
       </c>
       <c r="I44" t="n">
-        <v>12.43</v>
+        <v>10.59</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3761,10 +3791,10 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>34539.26</v>
+        <v>32052.42</v>
       </c>
       <c r="I45" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3829,10 +3859,10 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>41992.23</v>
+        <v>37514.4</v>
       </c>
       <c r="I46" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3881,7 +3911,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Modilon Province</t>
+          <t>Madang</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -3897,10 +3927,10 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>166476.11</v>
+        <v>149971.78</v>
       </c>
       <c r="I47" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3965,19 +3995,19 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>558228.67</v>
+        <v>83837.32000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>13.62</v>
+        <v>2.04</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Madang Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3986,7 +4016,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3032</v>
+        <v>0.08</v>
       </c>
       <c r="N48" t="n">
         <v>50.4</v>
@@ -4033,10 +4063,10 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>61350.49</v>
+        <v>57521.45</v>
       </c>
       <c r="I49" t="n">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -4101,10 +4131,10 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>51261.21</v>
+        <v>46448.62</v>
       </c>
       <c r="I50" t="n">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -4169,19 +4199,19 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>381229.34</v>
+        <v>52744.95</v>
       </c>
       <c r="I51" t="n">
-        <v>13.62</v>
+        <v>1.88</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Madang Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4190,7 +4220,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.3249</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N51" t="n">
         <v>40.5</v>
@@ -4237,10 +4267,10 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>133351.43</v>
+        <v>124427.8</v>
       </c>
       <c r="I52" t="n">
-        <v>11.11</v>
+        <v>10.37</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -4305,10 +4335,10 @@
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>185591.74</v>
+        <v>158172.3</v>
       </c>
       <c r="I53" t="n">
-        <v>13.26</v>
+        <v>11.3</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -4373,10 +4403,10 @@
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>197208.63</v>
+        <v>183870.58</v>
       </c>
       <c r="I54" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -4441,10 +4471,10 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>116532.37</v>
+        <v>108650.8</v>
       </c>
       <c r="I55" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -4509,10 +4539,10 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>98604.32000000001</v>
+        <v>91935.28999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4577,10 +4607,10 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>65352.72</v>
+        <v>65505.89</v>
       </c>
       <c r="I57" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4645,10 +4675,10 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>73953.24000000001</v>
+        <v>68951.47</v>
       </c>
       <c r="I58" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4713,10 +4743,10 @@
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>60507.19</v>
+        <v>56414.84</v>
       </c>
       <c r="I59" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4781,10 +4811,10 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>40845.45</v>
+        <v>40941.18</v>
       </c>
       <c r="I60" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4849,10 +4879,10 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>105327.34</v>
+        <v>98203.60000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4917,10 +4947,10 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>87399.28</v>
+        <v>81488.10000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4985,10 +5015,10 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>53784.17</v>
+        <v>50146.52</v>
       </c>
       <c r="I63" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -5053,10 +5083,10 @@
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>49302.16</v>
+        <v>45967.64</v>
       </c>
       <c r="I64" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -5121,10 +5151,10 @@
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>268388</v>
+        <v>228540.29</v>
       </c>
       <c r="I65" t="n">
-        <v>14.91</v>
+        <v>12.7</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -5189,10 +5219,10 @@
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>161983.05</v>
+        <v>151254.03</v>
       </c>
       <c r="I66" t="n">
-        <v>12.46</v>
+        <v>11.63</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -5257,10 +5287,10 @@
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>164014.89</v>
+        <v>139663.51</v>
       </c>
       <c r="I67" t="n">
-        <v>14.91</v>
+        <v>12.7</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -5325,10 +5355,10 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>144123.29</v>
+        <v>129163.42</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -5393,10 +5423,10 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>92084.83</v>
+        <v>82583.49000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -5461,19 +5491,19 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>517940.09</v>
+        <v>73481.47</v>
       </c>
       <c r="I70" t="n">
-        <v>13.63</v>
+        <v>1.93</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5482,7 +5512,7 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>0.3246</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N70" t="n">
         <v>40.5</v>
@@ -5523,22 +5553,37 @@
         <v>143.512</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>143.512</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>84449.8</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>2.06</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="O71" t="n">
         <v>0.3157</v>
@@ -5550,7 +5595,7 @@
         <v>4</v>
       </c>
       <c r="R71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -5576,22 +5621,37 @@
         <v>101.509</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>101.509</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>52975.83</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1.83</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="O72" t="n">
         <v>0.2688</v>
@@ -5603,7 +5663,7 @@
         <v>4</v>
       </c>
       <c r="R72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -5629,22 +5689,37 @@
         <v>112.01</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>112.01</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>60135.35</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1.88</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O73" t="n">
         <v>0.2794</v>
@@ -5656,7 +5731,7 @@
         <v>4</v>
       </c>
       <c r="R73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -5688,19 +5763,19 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>1144920.19</v>
+        <v>177001.22</v>
       </c>
       <c r="I74" t="n">
-        <v>13.63</v>
+        <v>2.11</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5709,7 +5784,7 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>0.3032</v>
+        <v>0.08</v>
       </c>
       <c r="N74" t="n">
         <v>81</v>
@@ -5756,19 +5831,19 @@
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>586090.1</v>
+        <v>94520.25</v>
       </c>
       <c r="I75" t="n">
-        <v>13.63</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5777,7 +5852,7 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>0.3032</v>
+        <v>0.08</v>
       </c>
       <c r="N75" t="n">
         <v>56.7</v>
@@ -5818,22 +5893,37 @@
         <v>108.509</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>108.509</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>66717.37</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>2.15</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O76" t="n">
         <v>0.3343</v>
@@ -5845,7 +5935,7 @@
         <v>4</v>
       </c>
       <c r="R76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -5871,22 +5961,37 @@
         <v>94.508</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>94.508</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>54269.35</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>2.01</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O77" t="n">
         <v>0.3057</v>
@@ -5898,7 +6003,7 @@
         <v>4</v>
       </c>
       <c r="R77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -5930,10 +6035,10 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>223680.52</v>
+        <v>190601.44</v>
       </c>
       <c r="I78" t="n">
-        <v>13.98</v>
+        <v>11.91</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -5998,10 +6103,10 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>158787.82</v>
+        <v>142296.47</v>
       </c>
       <c r="I79" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -6066,10 +6171,10 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>85898.21000000001</v>
+        <v>77013.09</v>
       </c>
       <c r="I80" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -6128,22 +6233,37 @@
         <v>126.011</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>126.011</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>66773.89999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1.85</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O81" t="n">
         <v>0.2745</v>
@@ -6155,7 +6275,7 @@
         <v>4</v>
       </c>
       <c r="R81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -6181,22 +6301,37 @@
         <v>136.512</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>136.512</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>75542.45</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1.94</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="O82" t="n">
         <v>0.291</v>
@@ -6208,7 +6343,7 @@
         <v>4</v>
       </c>
       <c r="R82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -6240,19 +6375,19 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>313490.05</v>
+        <v>44179.74</v>
       </c>
       <c r="I83" t="n">
-        <v>13.63</v>
+        <v>1.92</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6261,7 +6396,7 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0.3248</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N83" t="n">
         <v>40.5</v>
@@ -6302,22 +6437,37 @@
         <v>98.008</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>98.008</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>50218.58</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1.79</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O84" t="n">
         <v>0.2622</v>
@@ -6329,7 +6479,7 @@
         <v>4</v>
       </c>
       <c r="R84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -6361,10 +6511,10 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>196056.82</v>
+        <v>176854.83</v>
       </c>
       <c r="I85" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -6423,22 +6573,37 @@
         <v>119.01</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>119.01</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>57990.68</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1.71</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O86" t="n">
         <v>0.2445</v>
@@ -6450,7 +6615,7 @@
         <v>4</v>
       </c>
       <c r="R86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -6476,22 +6641,37 @@
         <v>108.509</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>108.509</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>53359</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1.72</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O87" t="n">
         <v>0.2476</v>
@@ -6503,7 +6683,7 @@
         <v>4</v>
       </c>
       <c r="R87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -6529,22 +6709,37 @@
         <v>77.00700000000001</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>77.00700000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>36556.35</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1.66</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O88" t="n">
         <v>0.2356</v>
@@ -6556,7 +6751,7 @@
         <v>4</v>
       </c>
       <c r="R88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -6588,10 +6783,10 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>47198.93</v>
+        <v>42368.8</v>
       </c>
       <c r="I89" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6656,10 +6851,10 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>111492.51</v>
+        <v>99985.36</v>
       </c>
       <c r="I90" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -6724,10 +6919,10 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>78054.55</v>
+        <v>70009.8</v>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -6792,10 +6987,10 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>88817</v>
+        <v>79672.91</v>
       </c>
       <c r="I92" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -6854,22 +7049,37 @@
         <v>84.00700000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>84.00700000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>43043</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1.79</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O93" t="n">
         <v>0.2622</v>
@@ -6881,7 +7091,7 @@
         <v>4</v>
       </c>
       <c r="R93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -6913,10 +7123,10 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>229707.53</v>
+        <v>195968.27</v>
       </c>
       <c r="I94" t="n">
-        <v>12.09</v>
+        <v>10.31</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -6981,10 +7191,10 @@
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>151327.61</v>
+        <v>135574.3</v>
       </c>
       <c r="I95" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -7049,10 +7259,10 @@
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>91049.94</v>
+        <v>81613.7</v>
       </c>
       <c r="I96" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -7111,22 +7321,37 @@
         <v>115.51</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>115.51</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>61740.93</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1.87</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O97" t="n">
         <v>0.2777</v>
@@ -7138,7 +7363,7 @@
         <v>4</v>
       </c>
       <c r="R97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -7170,10 +7395,10 @@
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>258848.95</v>
+        <v>220792.5</v>
       </c>
       <c r="I98" t="n">
-        <v>12.33</v>
+        <v>10.51</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -7238,10 +7463,10 @@
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>61274.77</v>
+        <v>54868.52</v>
       </c>
       <c r="I99" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -7300,22 +7525,37 @@
         <v>87.50700000000001</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>87.50700000000001</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>47683.21</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1.91</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M100" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O100" t="n">
         <v>0.285</v>
@@ -7327,7 +7567,7 @@
         <v>4</v>
       </c>
       <c r="R100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -7338,31 +7578,31 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Goroka Base Hospital</t>
+          <t>Goroka Provincial Hospital</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Goroka Province</t>
+          <t>Eastern Highlands</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>108000</v>
       </c>
       <c r="E101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="F101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>247560.66</v>
+        <v>220515.62</v>
       </c>
       <c r="I101" t="n">
-        <v>2.29</v>
+        <v>2.04</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -7427,10 +7667,10 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>129543.49</v>
+        <v>115542.95</v>
       </c>
       <c r="I102" t="n">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -7489,22 +7729,37 @@
         <v>119.01</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>119.01</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>69674.25999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Lae Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M103" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O103" t="n">
         <v>0.3389</v>
@@ -7516,7 +7771,7 @@
         <v>4</v>
       </c>
       <c r="R103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -7542,22 +7797,37 @@
         <v>108.509</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>108.509</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>68218.77</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>2.2</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Lae Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O104" t="n">
         <v>0.3693</v>
@@ -7569,7 +7839,7 @@
         <v>4</v>
       </c>
       <c r="R104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -7595,22 +7865,37 @@
         <v>98.008</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>98.008</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>57668.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>2.06</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Lae Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
       </c>
       <c r="M105" t="n">
-        <v>1</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O105" t="n">
         <v>0.341</v>
@@ -7622,7 +7907,7 @@
         <v>4</v>
       </c>
       <c r="R105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -7654,10 +7939,10 @@
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>167717.75</v>
+        <v>142842.1</v>
       </c>
       <c r="I106" t="n">
-        <v>12.9</v>
+        <v>10.99</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -7722,10 +8007,10 @@
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>141915.02</v>
+        <v>120866.39</v>
       </c>
       <c r="I107" t="n">
-        <v>12.9</v>
+        <v>10.99</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -7790,10 +8075,10 @@
         <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>98198.87</v>
+        <v>93842.8</v>
       </c>
       <c r="I108" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -7858,10 +8143,10 @@
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>25993.82</v>
+        <v>24840.74</v>
       </c>
       <c r="I109" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -7926,10 +8211,10 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>18773.31</v>
+        <v>17940.54</v>
       </c>
       <c r="I110" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -7994,10 +8279,10 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>15885.11</v>
+        <v>15180.45</v>
       </c>
       <c r="I111" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -8062,10 +8347,10 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>14441.01</v>
+        <v>13800.41</v>
       </c>
       <c r="I112" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -8114,7 +8399,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kavieng Province</t>
+          <t>New Ireland</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -8130,10 +8415,10 @@
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>140231.53</v>
+        <v>127177.59</v>
       </c>
       <c r="I113" t="n">
-        <v>2.42</v>
+        <v>2.19</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -8198,10 +8483,10 @@
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>111218.11</v>
+        <v>100864.99</v>
       </c>
       <c r="I114" t="n">
-        <v>2.42</v>
+        <v>2.19</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -8266,10 +8551,10 @@
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>46473.75</v>
+        <v>43492.4</v>
       </c>
       <c r="I115" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -8334,10 +8619,10 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>41102.34</v>
+        <v>37276.19</v>
       </c>
       <c r="I116" t="n">
-        <v>2.42</v>
+        <v>2.19</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -8402,10 +8687,10 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>19567.89</v>
+        <v>18312.59</v>
       </c>
       <c r="I117" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -8470,10 +8755,10 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>34243.82</v>
+        <v>32047.03</v>
       </c>
       <c r="I118" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -8538,10 +8823,10 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>178863.79</v>
+        <v>159531.81</v>
       </c>
       <c r="I119" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -8606,10 +8891,10 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>112977.6</v>
+        <v>101972.3</v>
       </c>
       <c r="I120" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -8674,10 +8959,10 @@
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>74320.78</v>
+        <v>66246.33</v>
       </c>
       <c r="I121" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -8742,10 +9027,10 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>40264.49</v>
+        <v>35965.72</v>
       </c>
       <c r="I122" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -8810,10 +9095,10 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>57057.61</v>
+        <v>53477.59</v>
       </c>
       <c r="I123" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -8878,10 +9163,10 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>44653.79</v>
+        <v>41852.03</v>
       </c>
       <c r="I124" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -8946,10 +9231,10 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>179523.4</v>
+        <v>162620.42</v>
       </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -9014,10 +9299,10 @@
         <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>73650.62</v>
+        <v>66716.07000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -9082,10 +9367,10 @@
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>37192.03</v>
+        <v>34610.99</v>
       </c>
       <c r="I127" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -9150,10 +9435,10 @@
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>94364.86</v>
+        <v>85479.97</v>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -9218,10 +9503,10 @@
         <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>55788.05</v>
+        <v>51916.49</v>
       </c>
       <c r="I129" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -9286,10 +9571,10 @@
         <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>164641.67</v>
+        <v>154156.04</v>
       </c>
       <c r="I130" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -9354,10 +9639,10 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>127781.59</v>
+        <v>119643.49</v>
       </c>
       <c r="I131" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -9422,10 +9707,10 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>108122.89</v>
+        <v>101236.8</v>
       </c>
       <c r="I132" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -9490,10 +9775,10 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>44232.09</v>
+        <v>41415.05</v>
       </c>
       <c r="I133" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -9558,10 +9843,10 @@
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>17201.37</v>
+        <v>16105.85</v>
       </c>
       <c r="I134" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -9626,10 +9911,10 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>39317.41</v>
+        <v>36813.38</v>
       </c>
       <c r="I135" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -9676,7 +9961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N116"/>
+  <dimension ref="A1:N135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -9687,7 +9972,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
@@ -9802,10 +10087,10 @@
         <v>42.0036</v>
       </c>
       <c r="H2" t="n">
-        <v>3211.1</v>
+        <v>2721.52</v>
       </c>
       <c r="I2" t="n">
-        <v>134877.92</v>
+        <v>114313.64</v>
       </c>
       <c r="J2" t="n">
         <v>100.39</v>
@@ -9854,10 +10139,10 @@
         <v>73.5063</v>
       </c>
       <c r="H3" t="n">
-        <v>189.77</v>
+        <v>195.25</v>
       </c>
       <c r="I3" t="n">
-        <v>13949.39</v>
+        <v>14351.95</v>
       </c>
       <c r="J3" t="n">
         <v>322.81</v>
@@ -9871,10 +10156,10 @@
         <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>294.81</v>
+        <v>271.69</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2493</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="4">
@@ -9912,10 +10197,10 @@
         <v>112.0096</v>
       </c>
       <c r="H4" t="n">
-        <v>189.77</v>
+        <v>195.25</v>
       </c>
       <c r="I4" t="n">
-        <v>21256.22</v>
+        <v>21869.64</v>
       </c>
       <c r="J4" t="n">
         <v>483.47</v>
@@ -9929,10 +10214,10 @@
         <v>0.55</v>
       </c>
       <c r="M4" t="n">
-        <v>449.23</v>
+        <v>413.99</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2493</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="5">
@@ -9970,10 +10255,10 @@
         <v>63.0054</v>
       </c>
       <c r="H5" t="n">
-        <v>189.77</v>
+        <v>195.25</v>
       </c>
       <c r="I5" t="n">
-        <v>11956.62</v>
+        <v>12301.67</v>
       </c>
       <c r="J5" t="n">
         <v>416.21</v>
@@ -9987,10 +10272,10 @@
         <v>0.55</v>
       </c>
       <c r="M5" t="n">
-        <v>252.69</v>
+        <v>232.87</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2493</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="6">
@@ -10028,10 +10313,10 @@
         <v>38.5033</v>
       </c>
       <c r="H6" t="n">
-        <v>3413.6</v>
+        <v>2892.77</v>
       </c>
       <c r="I6" t="n">
-        <v>131435.02</v>
+        <v>111381.19</v>
       </c>
       <c r="J6" t="n">
         <v>255.89</v>
@@ -10080,10 +10365,10 @@
         <v>154.0132</v>
       </c>
       <c r="H7" t="n">
-        <v>210.57</v>
+        <v>216.81</v>
       </c>
       <c r="I7" t="n">
-        <v>32431.32</v>
+        <v>33390.86</v>
       </c>
       <c r="J7" t="n">
         <v>538.08</v>
@@ -10097,10 +10382,10 @@
         <v>0.55</v>
       </c>
       <c r="M7" t="n">
-        <v>716.04</v>
+        <v>659.88</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2151</v>
+        <v>0.2334</v>
       </c>
     </row>
     <row r="8">
@@ -10138,10 +10423,10 @@
         <v>136.5117</v>
       </c>
       <c r="H8" t="n">
-        <v>177.03</v>
+        <v>200.68</v>
       </c>
       <c r="I8" t="n">
-        <v>24167.2</v>
+        <v>27395.41</v>
       </c>
       <c r="J8" t="n">
         <v>1162.1</v>
@@ -10155,10 +10440,10 @@
         <v>0.55</v>
       </c>
       <c r="M8" t="n">
-        <v>383.27</v>
+        <v>316.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3562</v>
+        <v>0.4317</v>
       </c>
     </row>
     <row r="9">
@@ -10196,10 +10481,10 @@
         <v>98.00839999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>177.03</v>
+        <v>200.68</v>
       </c>
       <c r="I9" t="n">
-        <v>17350.81</v>
+        <v>19668.5</v>
       </c>
       <c r="J9" t="n">
         <v>1251.46</v>
@@ -10213,10 +10498,10 @@
         <v>0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>275.17</v>
+        <v>227.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3562</v>
+        <v>0.4317</v>
       </c>
     </row>
     <row r="10">
@@ -10254,10 +10539,10 @@
         <v>108.5093</v>
       </c>
       <c r="H10" t="n">
-        <v>177.03</v>
+        <v>200.68</v>
       </c>
       <c r="I10" t="n">
-        <v>19209.83</v>
+        <v>21775.84</v>
       </c>
       <c r="J10" t="n">
         <v>767.52</v>
@@ -10271,10 +10556,10 @@
         <v>0.55</v>
       </c>
       <c r="M10" t="n">
-        <v>304.66</v>
+        <v>251.34</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3562</v>
+        <v>0.4317</v>
       </c>
     </row>
     <row r="11">
@@ -10312,10 +10597,10 @@
         <v>26.2522</v>
       </c>
       <c r="H11" t="n">
-        <v>177.03</v>
+        <v>200.68</v>
       </c>
       <c r="I11" t="n">
-        <v>4647.54</v>
+        <v>5268.35</v>
       </c>
       <c r="J11" t="n">
         <v>955.4400000000001</v>
@@ -10329,10 +10614,10 @@
         <v>0.55</v>
       </c>
       <c r="M11" t="n">
-        <v>73.70999999999999</v>
+        <v>60.81</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3562</v>
+        <v>0.4317</v>
       </c>
     </row>
     <row r="12">
@@ -10370,10 +10655,10 @@
         <v>31.5027</v>
       </c>
       <c r="H12" t="n">
-        <v>2953.6</v>
+        <v>2776.94</v>
       </c>
       <c r="I12" t="n">
-        <v>93046.5</v>
+        <v>87481</v>
       </c>
       <c r="J12" t="n">
         <v>617.75</v>
@@ -10422,10 +10707,10 @@
         <v>29.7525</v>
       </c>
       <c r="H13" t="n">
-        <v>2953.6</v>
+        <v>2776.94</v>
       </c>
       <c r="I13" t="n">
-        <v>87877.25</v>
+        <v>82620.95</v>
       </c>
       <c r="J13" t="n">
         <v>684.9400000000001</v>
@@ -10474,10 +10759,10 @@
         <v>217.0186</v>
       </c>
       <c r="H14" t="n">
-        <v>180.93</v>
+        <v>186.08</v>
       </c>
       <c r="I14" t="n">
-        <v>39264.72</v>
+        <v>40383.69</v>
       </c>
       <c r="J14" t="n">
         <v>448.61</v>
@@ -10491,10 +10776,10 @@
         <v>0.55</v>
       </c>
       <c r="M14" t="n">
-        <v>1105.7</v>
+        <v>1018.98</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1963</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="15">
@@ -10532,10 +10817,10 @@
         <v>59.5051</v>
       </c>
       <c r="H15" t="n">
-        <v>180.93</v>
+        <v>186.08</v>
       </c>
       <c r="I15" t="n">
-        <v>10766.13</v>
+        <v>11072.95</v>
       </c>
       <c r="J15" t="n">
         <v>358.09</v>
@@ -10549,10 +10834,10 @@
         <v>0.55</v>
       </c>
       <c r="M15" t="n">
-        <v>303.17</v>
+        <v>279.39</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1963</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="16">
@@ -10590,10 +10875,10 @@
         <v>101.5087</v>
       </c>
       <c r="H16" t="n">
-        <v>678.95</v>
+        <v>702.15</v>
       </c>
       <c r="I16" t="n">
-        <v>68919.02</v>
+        <v>71274.05</v>
       </c>
       <c r="J16" t="n">
         <v>534.23</v>
@@ -10607,10 +10892,10 @@
         <v>0.55</v>
       </c>
       <c r="M16" t="n">
-        <v>165.76</v>
+        <v>152.76</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6645</v>
       </c>
     </row>
     <row r="17">
@@ -10648,10 +10933,10 @@
         <v>73.5063</v>
       </c>
       <c r="H17" t="n">
-        <v>678.95</v>
+        <v>702.15</v>
       </c>
       <c r="I17" t="n">
-        <v>49906.88</v>
+        <v>51612.24</v>
       </c>
       <c r="J17" t="n">
         <v>758.5700000000001</v>
@@ -10665,10 +10950,10 @@
         <v>0.55</v>
       </c>
       <c r="M17" t="n">
-        <v>120.04</v>
+        <v>110.62</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6645</v>
       </c>
     </row>
     <row r="18">
@@ -10706,10 +10991,10 @@
         <v>84.0072</v>
       </c>
       <c r="H18" t="n">
-        <v>678.95</v>
+        <v>702.15</v>
       </c>
       <c r="I18" t="n">
-        <v>57036.43</v>
+        <v>58985.42</v>
       </c>
       <c r="J18" t="n">
         <v>483.91</v>
@@ -10723,10 +11008,10 @@
         <v>0.55</v>
       </c>
       <c r="M18" t="n">
-        <v>137.18</v>
+        <v>126.42</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6645</v>
       </c>
     </row>
     <row r="19">
@@ -10764,10 +11049,10 @@
         <v>49.0042</v>
       </c>
       <c r="H19" t="n">
-        <v>678.95</v>
+        <v>702.15</v>
       </c>
       <c r="I19" t="n">
-        <v>33271.25</v>
+        <v>34408.16</v>
       </c>
       <c r="J19" t="n">
         <v>488.03</v>
@@ -10781,10 +11066,10 @@
         <v>0.55</v>
       </c>
       <c r="M19" t="n">
-        <v>80.04000000000001</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6123</v>
+        <v>0.6644</v>
       </c>
     </row>
     <row r="20">
@@ -10822,10 +11107,10 @@
         <v>52.5045</v>
       </c>
       <c r="H20" t="n">
-        <v>678.95</v>
+        <v>702.15</v>
       </c>
       <c r="I20" t="n">
-        <v>35647.77</v>
+        <v>36865.89</v>
       </c>
       <c r="J20" t="n">
         <v>407.1</v>
@@ -10839,10 +11124,10 @@
         <v>0.55</v>
       </c>
       <c r="M20" t="n">
-        <v>85.73</v>
+        <v>79</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6125</v>
+        <v>0.6646</v>
       </c>
     </row>
     <row r="21">
@@ -10880,10 +11165,10 @@
         <v>248.5213</v>
       </c>
       <c r="H21" t="n">
-        <v>242.47</v>
+        <v>243.77</v>
       </c>
       <c r="I21" t="n">
-        <v>60259.28</v>
+        <v>60581.93</v>
       </c>
       <c r="J21" t="n">
         <v>323.36</v>
@@ -10897,10 +11182,10 @@
         <v>0.55</v>
       </c>
       <c r="M21" t="n">
-        <v>603.6799999999999</v>
+        <v>556.34</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4117</v>
+        <v>0.4467</v>
       </c>
     </row>
     <row r="22">
@@ -10938,10 +11223,10 @@
         <v>77.00660000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>242.47</v>
+        <v>243.77</v>
       </c>
       <c r="I22" t="n">
-        <v>18671.89</v>
+        <v>18771.86</v>
       </c>
       <c r="J22" t="n">
         <v>308.79</v>
@@ -10955,10 +11240,10 @@
         <v>0.55</v>
       </c>
       <c r="M22" t="n">
-        <v>187.05</v>
+        <v>172.38</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4117</v>
+        <v>0.4467</v>
       </c>
     </row>
     <row r="23">
@@ -10996,10 +11281,10 @@
         <v>45.5039</v>
       </c>
       <c r="H23" t="n">
-        <v>242.47</v>
+        <v>243.77</v>
       </c>
       <c r="I23" t="n">
-        <v>11033.39</v>
+        <v>11092.47</v>
       </c>
       <c r="J23" t="n">
         <v>447.3</v>
@@ -11013,10 +11298,10 @@
         <v>0.55</v>
       </c>
       <c r="M23" t="n">
-        <v>110.53</v>
+        <v>101.86</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4117</v>
+        <v>0.4467</v>
       </c>
     </row>
     <row r="24">
@@ -11054,10 +11339,10 @@
         <v>38.5033</v>
       </c>
       <c r="H24" t="n">
-        <v>242.47</v>
+        <v>243.77</v>
       </c>
       <c r="I24" t="n">
-        <v>9335.940000000001</v>
+        <v>9385.93</v>
       </c>
       <c r="J24" t="n">
         <v>459</v>
@@ -11071,10 +11356,10 @@
         <v>0.55</v>
       </c>
       <c r="M24" t="n">
-        <v>93.53</v>
+        <v>86.19</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4117</v>
+        <v>0.4467</v>
       </c>
     </row>
     <row r="25">
@@ -11112,10 +11397,10 @@
         <v>49.0042</v>
       </c>
       <c r="H25" t="n">
-        <v>242.47</v>
+        <v>243.77</v>
       </c>
       <c r="I25" t="n">
-        <v>11882.11</v>
+        <v>11945.73</v>
       </c>
       <c r="J25" t="n">
         <v>306.91</v>
@@ -11129,10 +11414,10 @@
         <v>0.55</v>
       </c>
       <c r="M25" t="n">
-        <v>119.03</v>
+        <v>109.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4117</v>
+        <v>0.4467</v>
       </c>
     </row>
     <row r="26">
@@ -11170,10 +11455,10 @@
         <v>35.003</v>
       </c>
       <c r="H26" t="n">
-        <v>3333.94</v>
+        <v>2829.85</v>
       </c>
       <c r="I26" t="n">
-        <v>116697.81</v>
+        <v>99053.38</v>
       </c>
       <c r="J26" t="n">
         <v>315.98</v>
@@ -11222,10 +11507,10 @@
         <v>147.0126</v>
       </c>
       <c r="H27" t="n">
-        <v>228.59</v>
+        <v>229.39</v>
       </c>
       <c r="I27" t="n">
-        <v>33605.72</v>
+        <v>33722.65</v>
       </c>
       <c r="J27" t="n">
         <v>117.11</v>
@@ -11239,10 +11524,10 @@
         <v>0.55</v>
       </c>
       <c r="M27" t="n">
-        <v>865.91</v>
+        <v>798</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1698</v>
+        <v>0.1842</v>
       </c>
     </row>
     <row r="28">
@@ -11280,10 +11565,10 @@
         <v>59.5051</v>
       </c>
       <c r="H28" t="n">
-        <v>228.59</v>
+        <v>229.39</v>
       </c>
       <c r="I28" t="n">
-        <v>13602.32</v>
+        <v>13649.65</v>
       </c>
       <c r="J28" t="n">
         <v>106.12</v>
@@ -11297,10 +11582,10 @@
         <v>0.55</v>
       </c>
       <c r="M28" t="n">
-        <v>350.47</v>
+        <v>322.98</v>
       </c>
       <c r="N28" t="n">
-        <v>0.1698</v>
+        <v>0.1842</v>
       </c>
     </row>
     <row r="29">
@@ -11338,10 +11623,10 @@
         <v>66.5057</v>
       </c>
       <c r="H29" t="n">
-        <v>3198.94</v>
+        <v>2715.69</v>
       </c>
       <c r="I29" t="n">
-        <v>212747.56</v>
+        <v>180608.68</v>
       </c>
       <c r="J29" t="n">
         <v>64.55</v>
@@ -11390,10 +11675,10 @@
         <v>91.0078</v>
       </c>
       <c r="H30" t="n">
-        <v>322.27</v>
+        <v>322.79</v>
       </c>
       <c r="I30" t="n">
-        <v>29329.28</v>
+        <v>29376.02</v>
       </c>
       <c r="J30" t="n">
         <v>106.06</v>
@@ -11407,10 +11692,10 @@
         <v>0.55</v>
       </c>
       <c r="M30" t="n">
-        <v>306.47</v>
+        <v>282.43</v>
       </c>
       <c r="N30" t="n">
-        <v>0.297</v>
+        <v>0.3222</v>
       </c>
     </row>
     <row r="31">
@@ -11448,10 +11733,10 @@
         <v>77.00660000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>313.82</v>
+        <v>293.91</v>
       </c>
       <c r="I31" t="n">
-        <v>24166.34</v>
+        <v>22633.26</v>
       </c>
       <c r="J31" t="n">
         <v>80.93000000000001</v>
@@ -11465,10 +11750,10 @@
         <v>0.55</v>
       </c>
       <c r="M31" t="n">
-        <v>274.55</v>
+        <v>298.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2805</v>
+        <v>0.2578</v>
       </c>
     </row>
     <row r="32">
@@ -11506,10 +11791,10 @@
         <v>42.0036</v>
       </c>
       <c r="H32" t="n">
-        <v>2822.91</v>
+        <v>2653.05</v>
       </c>
       <c r="I32" t="n">
-        <v>118572.41</v>
+        <v>111437.6</v>
       </c>
       <c r="J32" t="n">
         <v>98.78</v>
@@ -11558,10 +11843,10 @@
         <v>49.0042</v>
       </c>
       <c r="H33" t="n">
-        <v>3435.41</v>
+        <v>2918.47</v>
       </c>
       <c r="I33" t="n">
-        <v>168349.55</v>
+        <v>143017.07</v>
       </c>
       <c r="J33" t="n">
         <v>139.33</v>
@@ -11610,10 +11895,10 @@
         <v>308.0264</v>
       </c>
       <c r="H34" t="n">
-        <v>288.38</v>
+        <v>287.67</v>
       </c>
       <c r="I34" t="n">
-        <v>88829.14999999999</v>
+        <v>88609.14</v>
       </c>
       <c r="J34" t="n">
         <v>364.01</v>
@@ -11627,10 +11912,10 @@
         <v>0.55</v>
       </c>
       <c r="M34" t="n">
-        <v>364.92</v>
+        <v>336.29</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8441</v>
+        <v>0.9159</v>
       </c>
     </row>
     <row r="35">
@@ -11668,10 +11953,10 @@
         <v>182.0156</v>
       </c>
       <c r="H35" t="n">
-        <v>288.38</v>
+        <v>287.67</v>
       </c>
       <c r="I35" t="n">
-        <v>52489.95</v>
+        <v>52359.95</v>
       </c>
       <c r="J35" t="n">
         <v>428.56</v>
@@ -11685,10 +11970,10 @@
         <v>0.55</v>
       </c>
       <c r="M35" t="n">
-        <v>215.62</v>
+        <v>198.71</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8441</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="36">
@@ -11726,10 +12011,10 @@
         <v>154.0132</v>
       </c>
       <c r="H36" t="n">
-        <v>288.38</v>
+        <v>287.67</v>
       </c>
       <c r="I36" t="n">
-        <v>44414.58</v>
+        <v>44304.57</v>
       </c>
       <c r="J36" t="n">
         <v>280.66</v>
@@ -11743,10 +12028,10 @@
         <v>0.55</v>
       </c>
       <c r="M36" t="n">
-        <v>182.46</v>
+        <v>168.15</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8441</v>
+        <v>0.9159</v>
       </c>
     </row>
     <row r="37">
@@ -11784,10 +12069,10 @@
         <v>115.5099</v>
       </c>
       <c r="H37" t="n">
-        <v>288.38</v>
+        <v>287.67</v>
       </c>
       <c r="I37" t="n">
-        <v>33310.93</v>
+        <v>33228.43</v>
       </c>
       <c r="J37" t="n">
         <v>390.59</v>
@@ -11801,10 +12086,10 @@
         <v>0.55</v>
       </c>
       <c r="M37" t="n">
-        <v>136.84</v>
+        <v>126.11</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8441</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="38">
@@ -11842,10 +12127,10 @@
         <v>94.5081</v>
       </c>
       <c r="H38" t="n">
-        <v>288.38</v>
+        <v>287.67</v>
       </c>
       <c r="I38" t="n">
-        <v>27254.4</v>
+        <v>27186.9</v>
       </c>
       <c r="J38" t="n">
         <v>405.44</v>
@@ -11859,10 +12144,10 @@
         <v>0.55</v>
       </c>
       <c r="M38" t="n">
-        <v>111.97</v>
+        <v>103.18</v>
       </c>
       <c r="N38" t="n">
-        <v>0.8441</v>
+        <v>0.9159</v>
       </c>
     </row>
     <row r="39">
@@ -11900,10 +12185,10 @@
         <v>164.5141</v>
       </c>
       <c r="H39" t="n">
-        <v>288.38</v>
+        <v>287.67</v>
       </c>
       <c r="I39" t="n">
-        <v>47442.84</v>
+        <v>47325.34</v>
       </c>
       <c r="J39" t="n">
         <v>698.29</v>
@@ -11917,10 +12202,10 @@
         <v>0.55</v>
       </c>
       <c r="M39" t="n">
-        <v>194.89</v>
+        <v>179.61</v>
       </c>
       <c r="N39" t="n">
-        <v>0.8441</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="40">
@@ -11958,10 +12243,10 @@
         <v>136.5117</v>
       </c>
       <c r="H40" t="n">
-        <v>288.38</v>
+        <v>287.67</v>
       </c>
       <c r="I40" t="n">
-        <v>39367.47</v>
+        <v>39269.96</v>
       </c>
       <c r="J40" t="n">
         <v>544.61</v>
@@ -11975,10 +12260,10 @@
         <v>0.55</v>
       </c>
       <c r="M40" t="n">
-        <v>161.71</v>
+        <v>149.03</v>
       </c>
       <c r="N40" t="n">
-        <v>0.8442</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="41">
@@ -12016,10 +12301,10 @@
         <v>84.0072</v>
       </c>
       <c r="H41" t="n">
-        <v>288.38</v>
+        <v>287.67</v>
       </c>
       <c r="I41" t="n">
-        <v>24226.13</v>
+        <v>24166.13</v>
       </c>
       <c r="J41" t="n">
         <v>560.1</v>
@@ -12033,10 +12318,10 @@
         <v>0.55</v>
       </c>
       <c r="M41" t="n">
-        <v>99.53</v>
+        <v>91.72</v>
       </c>
       <c r="N41" t="n">
-        <v>0.844</v>
+        <v>0.9159</v>
       </c>
     </row>
     <row r="42">
@@ -12074,10 +12359,10 @@
         <v>77.00660000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>288.38</v>
+        <v>287.67</v>
       </c>
       <c r="I42" t="n">
-        <v>22207.29</v>
+        <v>22152.29</v>
       </c>
       <c r="J42" t="n">
         <v>494.37</v>
@@ -12091,10 +12376,10 @@
         <v>0.55</v>
       </c>
       <c r="M42" t="n">
-        <v>91.22</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>0.8442</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="43">
@@ -12132,10 +12417,10 @@
         <v>84.0072</v>
       </c>
       <c r="H43" t="n">
-        <v>426.09</v>
+        <v>470.5</v>
       </c>
       <c r="I43" t="n">
-        <v>35794.68</v>
+        <v>39525.49</v>
       </c>
       <c r="J43" t="n">
         <v>532.85</v>
@@ -12149,10 +12434,10 @@
         <v>0.55</v>
       </c>
       <c r="M43" t="n">
-        <v>156.79</v>
+        <v>129.35</v>
       </c>
       <c r="N43" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.6494</v>
       </c>
     </row>
     <row r="44">
@@ -12190,10 +12475,10 @@
         <v>52.5045</v>
       </c>
       <c r="H44" t="n">
-        <v>426.09</v>
+        <v>470.5</v>
       </c>
       <c r="I44" t="n">
-        <v>22371.68</v>
+        <v>24703.43</v>
       </c>
       <c r="J44" t="n">
         <v>426.83</v>
@@ -12207,10 +12492,10 @@
         <v>0.55</v>
       </c>
       <c r="M44" t="n">
-        <v>98.01000000000001</v>
+        <v>80.86</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5357</v>
+        <v>0.6494</v>
       </c>
     </row>
     <row r="45">
@@ -12248,10 +12533,10 @@
         <v>63.0054</v>
       </c>
       <c r="H45" t="n">
-        <v>3907.91</v>
+        <v>3318.05</v>
       </c>
       <c r="I45" t="n">
-        <v>246219.47</v>
+        <v>209055</v>
       </c>
       <c r="J45" t="n">
         <v>460.47</v>
@@ -12300,10 +12585,10 @@
         <v>45.5039</v>
       </c>
       <c r="H46" t="n">
-        <v>3207.91</v>
+        <v>3014.72</v>
       </c>
       <c r="I46" t="n">
-        <v>145972.44</v>
+        <v>137181.31</v>
       </c>
       <c r="J46" t="n">
         <v>538.6799999999999</v>
@@ -12352,10 +12637,10 @@
         <v>38.5033</v>
       </c>
       <c r="H47" t="n">
-        <v>3907.91</v>
+        <v>3318.05</v>
       </c>
       <c r="I47" t="n">
-        <v>150467.46</v>
+        <v>127755.83</v>
       </c>
       <c r="J47" t="n">
         <v>395.68</v>
@@ -12404,10 +12689,10 @@
         <v>56.0048</v>
       </c>
       <c r="H48" t="n">
-        <v>3642.1</v>
+        <v>3094.04</v>
       </c>
       <c r="I48" t="n">
-        <v>203975.16</v>
+        <v>173281.18</v>
       </c>
       <c r="J48" t="n">
         <v>201.21</v>
@@ -12456,10 +12741,10 @@
         <v>66.5057</v>
       </c>
       <c r="H49" t="n">
-        <v>3102.1</v>
+        <v>2637.37</v>
       </c>
       <c r="I49" t="n">
-        <v>206307.42</v>
+        <v>175400.46</v>
       </c>
       <c r="J49" t="n">
         <v>53.72</v>
@@ -12508,10 +12793,10 @@
         <v>73.5063</v>
       </c>
       <c r="H50" t="n">
-        <v>3169.6</v>
+        <v>2694.46</v>
       </c>
       <c r="I50" t="n">
-        <v>232985.67</v>
+        <v>198059.65</v>
       </c>
       <c r="J50" t="n">
         <v>94.98999999999999</v>
@@ -12560,10 +12845,10 @@
         <v>45.5039</v>
       </c>
       <c r="H51" t="n">
-        <v>3333.94</v>
+        <v>2829.85</v>
       </c>
       <c r="I51" t="n">
-        <v>151707.15</v>
+        <v>128769.39</v>
       </c>
       <c r="J51" t="n">
         <v>120.54</v>
@@ -12612,10 +12897,10 @@
         <v>38.5033</v>
       </c>
       <c r="H52" t="n">
-        <v>3333.94</v>
+        <v>2829.85</v>
       </c>
       <c r="I52" t="n">
-        <v>128367.59</v>
+        <v>108958.71</v>
       </c>
       <c r="J52" t="n">
         <v>130.5</v>
@@ -12664,10 +12949,10 @@
         <v>119.0102</v>
       </c>
       <c r="H53" t="n">
-        <v>473.28</v>
+        <v>479.26</v>
       </c>
       <c r="I53" t="n">
-        <v>56324.98</v>
+        <v>57037.25</v>
       </c>
       <c r="J53" t="n">
         <v>477.86</v>
@@ -12681,10 +12966,10 @@
         <v>0.55</v>
       </c>
       <c r="M53" t="n">
-        <v>197.68</v>
+        <v>182.17</v>
       </c>
       <c r="N53" t="n">
-        <v>0.602</v>
+        <v>0.6533</v>
       </c>
     </row>
     <row r="54">
@@ -12722,10 +13007,10 @@
         <v>31.5027</v>
       </c>
       <c r="H54" t="n">
-        <v>473.28</v>
+        <v>479.26</v>
       </c>
       <c r="I54" t="n">
-        <v>14909.55</v>
+        <v>15098.1</v>
       </c>
       <c r="J54" t="n">
         <v>482.12</v>
@@ -12739,10 +13024,10 @@
         <v>0.55</v>
       </c>
       <c r="M54" t="n">
-        <v>52.33</v>
+        <v>48.22</v>
       </c>
       <c r="N54" t="n">
-        <v>0.602</v>
+        <v>0.6533</v>
       </c>
     </row>
     <row r="55">
@@ -12780,10 +13065,10 @@
         <v>22.7519</v>
       </c>
       <c r="H55" t="n">
-        <v>473.28</v>
+        <v>479.26</v>
       </c>
       <c r="I55" t="n">
-        <v>10768.01</v>
+        <v>10904.18</v>
       </c>
       <c r="J55" t="n">
         <v>480.24</v>
@@ -12797,10 +13082,10 @@
         <v>0.55</v>
       </c>
       <c r="M55" t="n">
-        <v>37.79</v>
+        <v>34.83</v>
       </c>
       <c r="N55" t="n">
-        <v>0.602</v>
+        <v>0.6533</v>
       </c>
     </row>
     <row r="56">
@@ -12838,10 +13123,10 @@
         <v>19.2516</v>
       </c>
       <c r="H56" t="n">
-        <v>473.28</v>
+        <v>479.26</v>
       </c>
       <c r="I56" t="n">
-        <v>9111.389999999999</v>
+        <v>9226.610000000001</v>
       </c>
       <c r="J56" t="n">
         <v>481.26</v>
@@ -12855,10 +13140,10 @@
         <v>0.55</v>
       </c>
       <c r="M56" t="n">
-        <v>31.98</v>
+        <v>29.47</v>
       </c>
       <c r="N56" t="n">
-        <v>0.602</v>
+        <v>0.6533</v>
       </c>
     </row>
     <row r="57">
@@ -12896,10 +13181,10 @@
         <v>17.5015</v>
       </c>
       <c r="H57" t="n">
-        <v>473.28</v>
+        <v>479.26</v>
       </c>
       <c r="I57" t="n">
-        <v>8283.09</v>
+        <v>8387.83</v>
       </c>
       <c r="J57" t="n">
         <v>412.79</v>
@@ -12913,10 +13198,10 @@
         <v>0.55</v>
       </c>
       <c r="M57" t="n">
-        <v>29.07</v>
+        <v>26.79</v>
       </c>
       <c r="N57" t="n">
-        <v>0.602</v>
+        <v>0.6533</v>
       </c>
     </row>
     <row r="58">
@@ -12954,10 +13239,10 @@
         <v>203.0174</v>
       </c>
       <c r="H58" t="n">
-        <v>338.89</v>
+        <v>317.17</v>
       </c>
       <c r="I58" t="n">
-        <v>68799.60000000001</v>
+        <v>64391.64</v>
       </c>
       <c r="J58" t="n">
         <v>311.37</v>
@@ -12971,10 +13256,10 @@
         <v>0.55</v>
       </c>
       <c r="M58" t="n">
-        <v>583.09</v>
+        <v>634.38</v>
       </c>
       <c r="N58" t="n">
-        <v>0.3482</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="59">
@@ -13012,10 +13297,10 @@
         <v>161.0138</v>
       </c>
       <c r="H59" t="n">
-        <v>338.89</v>
+        <v>317.17</v>
       </c>
       <c r="I59" t="n">
-        <v>54565.2</v>
+        <v>51069.23</v>
       </c>
       <c r="J59" t="n">
         <v>94.95999999999999</v>
@@ -13029,10 +13314,10 @@
         <v>0.55</v>
       </c>
       <c r="M59" t="n">
-        <v>462.45</v>
+        <v>503.13</v>
       </c>
       <c r="N59" t="n">
-        <v>0.3482</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="60">
@@ -13070,10 +13355,10 @@
         <v>66.5057</v>
       </c>
       <c r="H60" t="n">
-        <v>346.94</v>
+        <v>344.7</v>
       </c>
       <c r="I60" t="n">
-        <v>23073.64</v>
+        <v>22924.59</v>
       </c>
       <c r="J60" t="n">
         <v>182.8</v>
@@ -13087,10 +13372,10 @@
         <v>0.55</v>
       </c>
       <c r="M60" t="n">
-        <v>180.39</v>
+        <v>166.24</v>
       </c>
       <c r="N60" t="n">
-        <v>0.3687</v>
+        <v>0.4001</v>
       </c>
     </row>
     <row r="61">
@@ -13128,10 +13413,10 @@
         <v>59.5051</v>
       </c>
       <c r="H61" t="n">
-        <v>338.89</v>
+        <v>317.17</v>
       </c>
       <c r="I61" t="n">
-        <v>20165.4</v>
+        <v>18873.41</v>
       </c>
       <c r="J61" t="n">
         <v>175.95</v>
@@ -13145,10 +13430,10 @@
         <v>0.55</v>
       </c>
       <c r="M61" t="n">
-        <v>170.93</v>
+        <v>185.96</v>
       </c>
       <c r="N61" t="n">
-        <v>0.3481</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="62">
@@ -13186,10 +13471,10 @@
         <v>28.0024</v>
       </c>
       <c r="H62" t="n">
-        <v>346.94</v>
+        <v>344.7</v>
       </c>
       <c r="I62" t="n">
-        <v>9715.219999999999</v>
+        <v>9652.459999999999</v>
       </c>
       <c r="J62" t="n">
         <v>205.12</v>
@@ -13203,10 +13488,10 @@
         <v>0.55</v>
       </c>
       <c r="M62" t="n">
-        <v>75.95</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>0.3687</v>
+        <v>0.4001</v>
       </c>
     </row>
     <row r="63">
@@ -13244,10 +13529,10 @@
         <v>49.0042</v>
       </c>
       <c r="H63" t="n">
-        <v>346.94</v>
+        <v>344.7</v>
       </c>
       <c r="I63" t="n">
-        <v>17001.63</v>
+        <v>16891.8</v>
       </c>
       <c r="J63" t="n">
         <v>368.78</v>
@@ -13261,10 +13546,10 @@
         <v>0.55</v>
       </c>
       <c r="M63" t="n">
-        <v>132.94</v>
+        <v>122.51</v>
       </c>
       <c r="N63" t="n">
-        <v>0.3686</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="64">
@@ -13302,10 +13587,10 @@
         <v>80.5069</v>
       </c>
       <c r="H64" t="n">
-        <v>356.88</v>
+        <v>355</v>
       </c>
       <c r="I64" t="n">
-        <v>28731.16</v>
+        <v>28579.72</v>
       </c>
       <c r="J64" t="n">
         <v>240.83</v>
@@ -13319,10 +13604,10 @@
         <v>0.55</v>
       </c>
       <c r="M64" t="n">
-        <v>89.37</v>
+        <v>82.36</v>
       </c>
       <c r="N64" t="n">
-        <v>0.9008</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="65">
@@ -13360,10 +13645,10 @@
         <v>63.0054</v>
       </c>
       <c r="H65" t="n">
-        <v>356.88</v>
+        <v>355</v>
       </c>
       <c r="I65" t="n">
-        <v>22485.26</v>
+        <v>22366.73</v>
       </c>
       <c r="J65" t="n">
         <v>189.94</v>
@@ -13377,10 +13662,10 @@
         <v>0.55</v>
       </c>
       <c r="M65" t="n">
-        <v>69.95</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9774</v>
       </c>
     </row>
     <row r="66">
@@ -13418,10 +13703,10 @@
         <v>273.0234</v>
       </c>
       <c r="H66" t="n">
-        <v>305.69</v>
+        <v>286.36</v>
       </c>
       <c r="I66" t="n">
-        <v>83459.77</v>
+        <v>78184.14999999999</v>
       </c>
       <c r="J66" t="n">
         <v>328.7</v>
@@ -13435,10 +13720,10 @@
         <v>0.55</v>
       </c>
       <c r="M66" t="n">
-        <v>527.98</v>
+        <v>574.42</v>
       </c>
       <c r="N66" t="n">
-        <v>0.5171</v>
+        <v>0.4753</v>
       </c>
     </row>
     <row r="67">
@@ -13476,10 +13761,10 @@
         <v>112.0096</v>
       </c>
       <c r="H67" t="n">
-        <v>305.69</v>
+        <v>286.36</v>
       </c>
       <c r="I67" t="n">
-        <v>34239.9</v>
+        <v>32075.55</v>
       </c>
       <c r="J67" t="n">
         <v>328.88</v>
@@ -13493,10 +13778,10 @@
         <v>0.55</v>
       </c>
       <c r="M67" t="n">
-        <v>216.6</v>
+        <v>235.66</v>
       </c>
       <c r="N67" t="n">
-        <v>0.5171</v>
+        <v>0.4753</v>
       </c>
     </row>
     <row r="68">
@@ -13534,10 +13819,10 @@
         <v>56.0048</v>
       </c>
       <c r="H68" t="n">
-        <v>312.24</v>
+        <v>308.74</v>
       </c>
       <c r="I68" t="n">
-        <v>17486.67</v>
+        <v>17290.73</v>
       </c>
       <c r="J68" t="n">
         <v>369.95</v>
@@ -13551,10 +13836,10 @@
         <v>0.55</v>
       </c>
       <c r="M68" t="n">
-        <v>102.28</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="N68" t="n">
-        <v>0.5475</v>
+        <v>0.5941</v>
       </c>
     </row>
     <row r="69">
@@ -13592,10 +13877,10 @@
         <v>143.5123</v>
       </c>
       <c r="H69" t="n">
-        <v>305.69</v>
+        <v>286.36</v>
       </c>
       <c r="I69" t="n">
-        <v>43869.88</v>
+        <v>41096.8</v>
       </c>
       <c r="J69" t="n">
         <v>215.37</v>
@@ -13609,10 +13894,10 @@
         <v>0.55</v>
       </c>
       <c r="M69" t="n">
-        <v>277.53</v>
+        <v>301.94</v>
       </c>
       <c r="N69" t="n">
-        <v>0.5171</v>
+        <v>0.4753</v>
       </c>
     </row>
     <row r="70">
@@ -13650,10 +13935,10 @@
         <v>84.0072</v>
       </c>
       <c r="H70" t="n">
-        <v>312.24</v>
+        <v>308.74</v>
       </c>
       <c r="I70" t="n">
-        <v>26230.01</v>
+        <v>25936.1</v>
       </c>
       <c r="J70" t="n">
         <v>445.5</v>
@@ -13667,10 +13952,10 @@
         <v>0.55</v>
       </c>
       <c r="M70" t="n">
-        <v>153.44</v>
+        <v>141.4</v>
       </c>
       <c r="N70" t="n">
-        <v>0.5475</v>
+        <v>0.5941</v>
       </c>
     </row>
     <row r="71">
@@ -13708,10 +13993,10 @@
         <v>234.5201</v>
       </c>
       <c r="H71" t="n">
-        <v>350.19</v>
+        <v>348.06</v>
       </c>
       <c r="I71" t="n">
-        <v>82125.48</v>
+        <v>81627.44</v>
       </c>
       <c r="J71" t="n">
         <v>357.34</v>
@@ -13725,10 +14010,10 @@
         <v>0.55</v>
       </c>
       <c r="M71" t="n">
-        <v>406.46</v>
+        <v>374.58</v>
       </c>
       <c r="N71" t="n">
-        <v>0.577</v>
+        <v>0.6261</v>
       </c>
     </row>
     <row r="72">
@@ -13766,10 +14051,10 @@
         <v>182.0156</v>
       </c>
       <c r="H72" t="n">
-        <v>350.19</v>
+        <v>348.06</v>
       </c>
       <c r="I72" t="n">
-        <v>63739.18</v>
+        <v>63352.64</v>
       </c>
       <c r="J72" t="n">
         <v>513.78</v>
@@ -13783,10 +14068,10 @@
         <v>0.55</v>
       </c>
       <c r="M72" t="n">
-        <v>315.46</v>
+        <v>290.72</v>
       </c>
       <c r="N72" t="n">
-        <v>0.577</v>
+        <v>0.6261</v>
       </c>
     </row>
     <row r="73">
@@ -13824,10 +14109,10 @@
         <v>154.0132</v>
       </c>
       <c r="H73" t="n">
-        <v>350.19</v>
+        <v>348.06</v>
       </c>
       <c r="I73" t="n">
-        <v>53933.15</v>
+        <v>53606.08</v>
       </c>
       <c r="J73" t="n">
         <v>577.77</v>
@@ -13841,10 +14126,10 @@
         <v>0.55</v>
       </c>
       <c r="M73" t="n">
-        <v>266.93</v>
+        <v>246</v>
       </c>
       <c r="N73" t="n">
-        <v>0.577</v>
+        <v>0.6261</v>
       </c>
     </row>
     <row r="74">
@@ -13882,10 +14167,10 @@
         <v>63.0054</v>
       </c>
       <c r="H74" t="n">
-        <v>350.19</v>
+        <v>348.06</v>
       </c>
       <c r="I74" t="n">
-        <v>22063.56</v>
+        <v>21929.76</v>
       </c>
       <c r="J74" t="n">
         <v>447.68</v>
@@ -13899,10 +14184,10 @@
         <v>0.55</v>
       </c>
       <c r="M74" t="n">
-        <v>109.19</v>
+        <v>100.63</v>
       </c>
       <c r="N74" t="n">
-        <v>0.577</v>
+        <v>0.6261</v>
       </c>
     </row>
     <row r="75">
@@ -13940,10 +14225,10 @@
         <v>24.5021</v>
       </c>
       <c r="H75" t="n">
-        <v>350.19</v>
+        <v>348.06</v>
       </c>
       <c r="I75" t="n">
-        <v>8580.27</v>
+        <v>8528.24</v>
       </c>
       <c r="J75" t="n">
         <v>267.72</v>
@@ -13957,10 +14242,10 @@
         <v>0.55</v>
       </c>
       <c r="M75" t="n">
-        <v>42.47</v>
+        <v>39.14</v>
       </c>
       <c r="N75" t="n">
-        <v>0.577</v>
+        <v>0.6261</v>
       </c>
     </row>
     <row r="76">
@@ -13998,10 +14283,10 @@
         <v>56.0048</v>
       </c>
       <c r="H76" t="n">
-        <v>350.19</v>
+        <v>348.06</v>
       </c>
       <c r="I76" t="n">
-        <v>19612.05</v>
+        <v>19493.12</v>
       </c>
       <c r="J76" t="n">
         <v>370.08</v>
@@ -14015,10 +14300,10 @@
         <v>0.55</v>
       </c>
       <c r="M76" t="n">
-        <v>97.06</v>
+        <v>89.45</v>
       </c>
       <c r="N76" t="n">
-        <v>0.577</v>
+        <v>0.6261</v>
       </c>
     </row>
     <row r="77">
@@ -14053,13 +14338,13 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>587.5544</v>
+        <v>588.0504</v>
       </c>
       <c r="H77" t="n">
         <v>55.64</v>
       </c>
       <c r="I77" t="n">
-        <v>32691.99</v>
+        <v>32716.97</v>
       </c>
       <c r="J77" t="n">
         <v>4.28</v>
@@ -14108,10 +14393,10 @@
         <v>462.0396</v>
       </c>
       <c r="H78" t="n">
-        <v>60.04</v>
+        <v>60.03</v>
       </c>
       <c r="I78" t="n">
-        <v>27738.74</v>
+        <v>27738.47</v>
       </c>
       <c r="J78" t="n">
         <v>13.54</v>
@@ -14163,7 +14448,7 @@
         <v>54.32</v>
       </c>
       <c r="I79" t="n">
-        <v>11598.56</v>
+        <v>11598.44</v>
       </c>
       <c r="J79" t="n">
         <v>1.51</v>
@@ -14215,7 +14500,7 @@
         <v>56.12</v>
       </c>
       <c r="I80" t="n">
-        <v>10606.96</v>
+        <v>10606.85</v>
       </c>
       <c r="J80" t="n">
         <v>5.29</v>
@@ -14267,7 +14552,7 @@
         <v>58.93</v>
       </c>
       <c r="I81" t="n">
-        <v>7838.18</v>
+        <v>7838.11</v>
       </c>
       <c r="J81" t="n">
         <v>11.21</v>
@@ -14316,10 +14601,10 @@
         <v>164.5141</v>
       </c>
       <c r="H82" t="n">
-        <v>128.3</v>
+        <v>110.15</v>
       </c>
       <c r="I82" t="n">
-        <v>21106.9</v>
+        <v>18120.47</v>
       </c>
       <c r="J82" t="n">
         <v>103.3</v>
@@ -14336,7 +14621,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LN-PNG-CEN-004-ROAD</t>
+          <t>LN-PNG-CEN-002-ROAD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -14346,7 +14631,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PNG-CEN-004</t>
+          <t>PNG-CEN-002</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -14365,16 +14650,16 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>133.0114</v>
+        <v>147.0126</v>
       </c>
       <c r="H83" t="n">
-        <v>181.76</v>
+        <v>171.81</v>
       </c>
       <c r="I83" t="n">
-        <v>24175.85</v>
+        <v>25258.46</v>
       </c>
       <c r="J83" t="n">
-        <v>183.69</v>
+        <v>171.76</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -14388,7 +14673,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LN-PNG-GUL-001-ROAD</t>
+          <t>LN-PNG-CEN-003-ROAD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -14398,7 +14683,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PNG-GUL-001</t>
+          <t>PNG-CEN-003</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -14417,16 +14702,16 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>203.0174</v>
+        <v>66.5057</v>
       </c>
       <c r="H84" t="n">
-        <v>279.83</v>
+        <v>187.28</v>
       </c>
       <c r="I84" t="n">
-        <v>56810.76</v>
+        <v>12455.04</v>
       </c>
       <c r="J84" t="n">
-        <v>331.17</v>
+        <v>218.82</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -14440,17 +14725,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LN-PNG-MOR-001-ROAD</t>
+          <t>LN-PNG-CEN-004-ROAD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AMS-LAE</t>
+          <t>AMS-POM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PNG-MOR-001</t>
+          <t>PNG-CEN-004</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14460,7 +14745,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lae Area Medical Store road distribution</t>
+          <t>Port Moresby Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -14469,16 +14754,16 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>656.3203999999999</v>
+        <v>133.0114</v>
       </c>
       <c r="H85" t="n">
-        <v>109.45</v>
+        <v>152.79</v>
       </c>
       <c r="I85" t="n">
-        <v>71836.2</v>
+        <v>20322.22</v>
       </c>
       <c r="J85" t="n">
-        <v>1.06</v>
+        <v>183.69</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -14492,17 +14777,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LN-PNG-MOR-002-ROAD</t>
+          <t>LN-PNG-CEN-006-ROAD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AMS-LAE</t>
+          <t>AMS-POM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PNG-MOR-002</t>
+          <t>PNG-CEN-006</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14512,7 +14797,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lae Area Medical Store road distribution</t>
+          <t>Port Moresby Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -14521,16 +14806,16 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>189.0162</v>
+        <v>56.0048</v>
       </c>
       <c r="H86" t="n">
-        <v>176.57</v>
+        <v>141.81</v>
       </c>
       <c r="I86" t="n">
-        <v>33374.51</v>
+        <v>7941.92</v>
       </c>
       <c r="J86" t="n">
-        <v>113.39</v>
+        <v>125.96</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -14544,17 +14829,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LN-PNG-MOR-008-ROAD</t>
+          <t>LN-PNG-GUL-001-ROAD</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AMS-LAE</t>
+          <t>AMS-POM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PNG-MOR-008</t>
+          <t>PNG-GUL-001</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14564,7 +14849,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lae Area Medical Store road distribution</t>
+          <t>Port Moresby Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -14573,16 +14858,16 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>80.5069</v>
+        <v>203.0174</v>
       </c>
       <c r="H87" t="n">
-        <v>169.75</v>
+        <v>231.01</v>
       </c>
       <c r="I87" t="n">
-        <v>13665.78</v>
+        <v>46899.34</v>
       </c>
       <c r="J87" t="n">
-        <v>101.42</v>
+        <v>331.17</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -14596,17 +14881,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LN-PNG-MAD-001-ROAD</t>
+          <t>LN-PNG-GUL-005-ROAD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AMS-MAD</t>
+          <t>AMS-POM</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PNG-MAD-001</t>
+          <t>PNG-GUL-005</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14616,7 +14901,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Madang Area Medical Store road distribution</t>
+          <t>Port Moresby Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -14625,16 +14910,16 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>336.0288</v>
+        <v>84.0072</v>
       </c>
       <c r="H88" t="n">
-        <v>143.57</v>
+        <v>240.29</v>
       </c>
       <c r="I88" t="n">
-        <v>48243.95</v>
+        <v>20186.05</v>
       </c>
       <c r="J88" t="n">
-        <v>1.39</v>
+        <v>276.29</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -14648,17 +14933,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>LN-PNG-ENG-001-ROAD</t>
+          <t>LN-PNG-MOR-001-ROAD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AMS-HGN</t>
+          <t>AMS-LAE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PNG-ENG-001</t>
+          <t>PNG-MOR-001</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14668,7 +14953,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mount Hagen Area Medical Store road distribution</t>
+          <t>Lae Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -14677,16 +14962,16 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>252.0216</v>
+        <v>658.0564000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>220.02</v>
+        <v>105.36</v>
       </c>
       <c r="I89" t="n">
-        <v>55449.17</v>
+        <v>69331.11</v>
       </c>
       <c r="J89" t="n">
-        <v>122.66</v>
+        <v>1.06</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -14700,17 +14985,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LN-PNG-ENG-002-ROAD</t>
+          <t>LN-PNG-MOR-002-ROAD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AMS-HGN</t>
+          <t>AMS-LAE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PNG-ENG-002</t>
+          <t>PNG-MOR-002</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14720,7 +15005,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mount Hagen Area Medical Store road distribution</t>
+          <t>Lae Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -14729,16 +15014,16 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>168.0144</v>
+        <v>189.0162</v>
       </c>
       <c r="H90" t="n">
-        <v>196.23</v>
+        <v>162.73</v>
       </c>
       <c r="I90" t="n">
-        <v>32968.75</v>
+        <v>30758.79</v>
       </c>
       <c r="J90" t="n">
-        <v>80.92</v>
+        <v>113.39</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -14752,17 +15037,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LN-PNG-SHP-001-ROAD</t>
+          <t>LN-PNG-MOR-003-ROAD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AMS-HGN</t>
+          <t>AMS-LAE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PNG-SHP-001</t>
+          <t>PNG-MOR-003</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14772,7 +15057,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mount Hagen Area Medical Store road distribution</t>
+          <t>Lae Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -14781,16 +15066,16 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>276.5237</v>
+        <v>108.5093</v>
       </c>
       <c r="H91" t="n">
-        <v>222.38</v>
+        <v>185.55</v>
       </c>
       <c r="I91" t="n">
-        <v>61492.6</v>
+        <v>20134.32</v>
       </c>
       <c r="J91" t="n">
-        <v>126.8</v>
+        <v>129.6</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -14804,17 +15089,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LN-PNG-SHP-002-ROAD</t>
+          <t>LN-PNG-MOR-005-ROAD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AMS-HGN</t>
+          <t>AMS-LAE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PNG-SHP-002</t>
+          <t>PNG-MOR-005</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -14824,7 +15109,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mount Hagen Area Medical Store road distribution</t>
+          <t>Lae Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -14833,16 +15118,16 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>154.0132</v>
+        <v>126.0108</v>
       </c>
       <c r="H92" t="n">
-        <v>205.88</v>
+        <v>232.99</v>
       </c>
       <c r="I92" t="n">
-        <v>31708.47</v>
+        <v>29359.08</v>
       </c>
       <c r="J92" t="n">
-        <v>97.86</v>
+        <v>209.49</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -14856,17 +15141,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LN-PNG-WHP-001-ROAD</t>
+          <t>LN-PNG-MOR-008-ROAD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AMS-HGN</t>
+          <t>AMS-LAE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PNG-WHP-001</t>
+          <t>PNG-MOR-008</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -14876,7 +15161,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mount Hagen Area Medical Store road distribution</t>
+          <t>Lae Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -14885,16 +15170,16 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>392.0336</v>
+        <v>80.5069</v>
       </c>
       <c r="H93" t="n">
-        <v>148.25</v>
+        <v>156.71</v>
       </c>
       <c r="I93" t="n">
-        <v>58119.31</v>
+        <v>12616.52</v>
       </c>
       <c r="J93" t="n">
-        <v>2.42</v>
+        <v>101.42</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -14908,17 +15193,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LN-PNG-WHP-005-ROAD</t>
+          <t>LN-PNG-MAD-001-ROAD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AMS-HGN</t>
+          <t>AMS-MAD</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PNG-WHP-005</t>
+          <t>PNG-MAD-001</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -14928,7 +15213,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mount Hagen Area Medical Store road distribution</t>
+          <t>Madang Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -14937,16 +15222,16 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>91.0078</v>
+        <v>336.0288</v>
       </c>
       <c r="H94" t="n">
-        <v>166.77</v>
+        <v>137.04</v>
       </c>
       <c r="I94" t="n">
-        <v>15177.72</v>
+        <v>46050.21</v>
       </c>
       <c r="J94" t="n">
-        <v>29.25</v>
+        <v>1.39</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -14960,17 +15245,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LN-PNG-JIW-001-ROAD</t>
+          <t>LN-PNG-MAD-002-ROAD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AMS-HGN</t>
+          <t>AMS-MAD</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PNG-JIW-001</t>
+          <t>PNG-MAD-002</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -14980,7 +15265,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mount Hagen Area Medical Store road distribution</t>
+          <t>Madang Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -14989,16 +15274,16 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>203.0174</v>
+        <v>143.5123</v>
       </c>
       <c r="H95" t="n">
-        <v>197.33</v>
+        <v>274.92</v>
       </c>
       <c r="I95" t="n">
-        <v>40060.58</v>
+        <v>39454.15</v>
       </c>
       <c r="J95" t="n">
-        <v>82.84999999999999</v>
+        <v>202.79</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -15012,17 +15297,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LN-PNG-JIW-002-ROAD</t>
+          <t>LN-PNG-MAD-005-ROAD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AMS-HGN</t>
+          <t>AMS-MAD</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PNG-JIW-002</t>
+          <t>PNG-MAD-005</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15032,7 +15317,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mount Hagen Area Medical Store road distribution</t>
+          <t>Madang Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -15041,16 +15326,16 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>143.5123</v>
+        <v>98.00839999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>192.04</v>
+        <v>228.9</v>
       </c>
       <c r="I96" t="n">
-        <v>27559.56</v>
+        <v>22434.49</v>
       </c>
       <c r="J96" t="n">
-        <v>73.56999999999999</v>
+        <v>132.55</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -15064,7 +15349,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LN-PNG-JIW-003-ROAD</t>
+          <t>LN-PNG-ENG-001-ROAD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -15074,7 +15359,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PNG-JIW-003</t>
+          <t>PNG-ENG-001</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15093,16 +15378,16 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>164.5141</v>
+        <v>252.0216</v>
       </c>
       <c r="H97" t="n">
-        <v>188.02</v>
+        <v>203.25</v>
       </c>
       <c r="I97" t="n">
-        <v>30932.51</v>
+        <v>51222.24</v>
       </c>
       <c r="J97" t="n">
-        <v>66.53</v>
+        <v>122.66</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -15116,7 +15401,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LN-PNG-CHM-001-ROAD</t>
+          <t>LN-PNG-ENG-002-ROAD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -15126,7 +15411,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PNG-CHM-001</t>
+          <t>PNG-ENG-002</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15145,16 +15430,16 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>259.0222</v>
+        <v>168.0144</v>
       </c>
       <c r="H98" t="n">
-        <v>232.38</v>
+        <v>182.26</v>
       </c>
       <c r="I98" t="n">
-        <v>60190.32</v>
+        <v>30622.71</v>
       </c>
       <c r="J98" t="n">
-        <v>144.34</v>
+        <v>80.92</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -15168,7 +15453,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LN-PNG-CHM-002-ROAD</t>
+          <t>LN-PNG-ENG-003-ROAD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -15178,7 +15463,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PNG-CHM-002</t>
+          <t>PNG-ENG-003</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -15197,16 +15482,16 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>161.0138</v>
+        <v>133.0114</v>
       </c>
       <c r="H99" t="n">
-        <v>213.63</v>
+        <v>243.18</v>
       </c>
       <c r="I99" t="n">
-        <v>34397.03</v>
+        <v>32345.85</v>
       </c>
       <c r="J99" t="n">
-        <v>111.45</v>
+        <v>166.27</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -15220,7 +15505,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LN-PNG-CHM-005-ROAD</t>
+          <t>LN-PNG-ENG-004-ROAD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -15230,7 +15515,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PNG-CHM-005</t>
+          <t>PNG-ENG-004</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -15249,16 +15534,16 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>101.5087</v>
+        <v>143.5123</v>
       </c>
       <c r="H100" t="n">
-        <v>251.79</v>
+        <v>279.19</v>
       </c>
       <c r="I100" t="n">
-        <v>25558.81</v>
+        <v>40066.63</v>
       </c>
       <c r="J100" t="n">
-        <v>178.4</v>
+        <v>226.91</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -15272,17 +15557,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LN-PNG-EHP-001-ROAD</t>
+          <t>LN-PNG-ENG-005-ROAD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AMS-LAE</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PNG-EHP-001</t>
+          <t>PNG-ENG-005</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -15292,7 +15577,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lae Area Medical Store road distribution</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -15301,16 +15586,16 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>378.1564</v>
+        <v>101.5087</v>
       </c>
       <c r="H101" t="n">
-        <v>302.8</v>
+        <v>212.62</v>
       </c>
       <c r="I101" t="n">
-        <v>114505.86</v>
+        <v>21582.85</v>
       </c>
       <c r="J101" t="n">
-        <v>334.85</v>
+        <v>114.8</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -15324,17 +15609,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LN-PNG-EHP-002-ROAD</t>
+          <t>LN-PNG-ENG-006-ROAD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AMS-LAE</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PNG-EHP-002</t>
+          <t>PNG-ENG-006</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -15344,7 +15629,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lae Area Medical Store road distribution</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -15353,16 +15638,16 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>217.0186</v>
+        <v>112.0096</v>
       </c>
       <c r="H102" t="n">
-        <v>245.07</v>
+        <v>227.61</v>
       </c>
       <c r="I102" t="n">
-        <v>53185.22</v>
+        <v>25494.83</v>
       </c>
       <c r="J102" t="n">
-        <v>233.57</v>
+        <v>140.05</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -15376,17 +15661,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LN-PNG-ENB-001-ROAD</t>
+          <t>LN-PNG-HEL-001-ROAD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AMS-KOK</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PNG-ENB-001</t>
+          <t>PNG-HEL-001</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -15396,7 +15681,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kokopo Area Medical Store road distribution</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -15405,16 +15690,16 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>322.0276</v>
+        <v>294.0252</v>
       </c>
       <c r="H103" t="n">
-        <v>203.58</v>
+        <v>292.73</v>
       </c>
       <c r="I103" t="n">
-        <v>65557.97</v>
+        <v>86069.84</v>
       </c>
       <c r="J103" t="n">
-        <v>31.5</v>
+        <v>249.72</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -15428,17 +15713,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LN-PNG-ENB-002-ROAD</t>
+          <t>LN-PNG-HEL-002-ROAD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AMS-KOK</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PNG-ENB-002</t>
+          <t>PNG-HEL-002</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15448,7 +15733,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kokopo Area Medical Store road distribution</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -15457,16 +15742,16 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>213.5183</v>
+        <v>150.5129</v>
       </c>
       <c r="H104" t="n">
-        <v>177.27</v>
+        <v>318.72</v>
       </c>
       <c r="I104" t="n">
-        <v>37850.92</v>
+        <v>47972.05</v>
       </c>
       <c r="J104" t="n">
-        <v>1.35</v>
+        <v>293.5</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -15480,17 +15765,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LN-PNG-ENB-003-ROAD</t>
+          <t>LN-PNG-HEL-003-ROAD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AMS-KOK</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PNG-ENB-003</t>
+          <t>PNG-HEL-003</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15500,7 +15785,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kokopo Area Medical Store road distribution</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -15509,16 +15794,16 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>133.0114</v>
+        <v>108.5093</v>
       </c>
       <c r="H105" t="n">
-        <v>206.9</v>
+        <v>305.59</v>
       </c>
       <c r="I105" t="n">
-        <v>27520.56</v>
+        <v>33159.37</v>
       </c>
       <c r="J105" t="n">
-        <v>36.5</v>
+        <v>271.38</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -15532,17 +15817,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LN-PNG-ENB-004-ROAD</t>
+          <t>LN-PNG-HEL-004-ROAD</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AMS-KOK</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PNG-ENB-004</t>
+          <t>PNG-HEL-004</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15552,7 +15837,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kokopo Area Medical Store road distribution</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -15561,16 +15846,16 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>73.5063</v>
+        <v>94.5081</v>
       </c>
       <c r="H106" t="n">
-        <v>195.92</v>
+        <v>264.97</v>
       </c>
       <c r="I106" t="n">
-        <v>14401.2</v>
+        <v>25041.41</v>
       </c>
       <c r="J106" t="n">
-        <v>19.98</v>
+        <v>202.96</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -15584,27 +15869,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LN-PNG-GUL-005-AIRFB</t>
+          <t>LN-PNG-SHP-001-ROAD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AMS-POM</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PNG-GUL-005</t>
+          <t>PNG-SHP-001</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -15613,50 +15898,50 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>84.0072</v>
+        <v>276.5237</v>
       </c>
       <c r="H107" t="n">
-        <v>3448.6</v>
+        <v>205.33</v>
       </c>
       <c r="I107" t="n">
-        <v>289707.56</v>
+        <v>56777.68</v>
       </c>
       <c r="J107" t="n">
-        <v>190.55</v>
+        <v>126.8</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>great_circle</t>
+          <t>detour_factor</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LN-PNG-CEN-002-AIRFB</t>
+          <t>LN-PNG-SHP-002-ROAD</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AMS-POM</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PNG-CEN-002</t>
+          <t>PNG-SHP-002</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -15665,50 +15950,50 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>147.0126</v>
+        <v>154.0132</v>
       </c>
       <c r="H108" t="n">
-        <v>3448.6</v>
+        <v>190.78</v>
       </c>
       <c r="I108" t="n">
-        <v>506988.23</v>
+        <v>29382.37</v>
       </c>
       <c r="J108" t="n">
-        <v>118.45</v>
+        <v>97.86</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>great_circle</t>
+          <t>detour_factor</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LN-PNG-CEN-006-AIRFB</t>
+          <t>LN-PNG-SHP-003-ROAD</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AMS-POM</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PNG-CEN-006</t>
+          <t>PNG-SHP-003</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -15717,50 +16002,50 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>56.0048</v>
+        <v>126.0108</v>
       </c>
       <c r="H109" t="n">
-        <v>3448.6</v>
+        <v>220.64</v>
       </c>
       <c r="I109" t="n">
-        <v>193138.37</v>
+        <v>27803.31</v>
       </c>
       <c r="J109" t="n">
-        <v>86.87</v>
+        <v>128.31</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>great_circle</t>
+          <t>detour_factor</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LN-PNG-MAD-002-AIRFB</t>
+          <t>LN-PNG-SHP-004-ROAD</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AMS-MAD</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PNG-MAD-002</t>
+          <t>PNG-SHP-004</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -15769,50 +16054,50 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>143.5123</v>
+        <v>136.5117</v>
       </c>
       <c r="H110" t="n">
-        <v>3537.91</v>
+        <v>244.11</v>
       </c>
       <c r="I110" t="n">
-        <v>507733.69</v>
+        <v>33324.31</v>
       </c>
       <c r="J110" t="n">
-        <v>139.86</v>
+        <v>167.84</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>great_circle</t>
+          <t>detour_factor</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LN-PNG-MAD-005-AIRFB</t>
+          <t>LN-PNG-SHP-005-ROAD</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AMS-MAD</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PNG-MAD-005</t>
+          <t>PNG-SHP-005</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -15821,50 +16106,50 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>98.00839999999999</v>
+        <v>80.5069</v>
       </c>
       <c r="H111" t="n">
-        <v>3537.91</v>
+        <v>239.51</v>
       </c>
       <c r="I111" t="n">
-        <v>346744.96</v>
+        <v>19281.86</v>
       </c>
       <c r="J111" t="n">
-        <v>75.73999999999999</v>
+        <v>160.08</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>great_circle</t>
+          <t>detour_factor</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LN-PNG-CEN-003-AIRFB</t>
+          <t>LN-PNG-SHP-006-ROAD</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AMS-POM</t>
+          <t>AMS-HGN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PNG-CEN-003</t>
+          <t>PNG-SHP-006</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -15873,30 +16158,30 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>66.5057</v>
+        <v>98.00839999999999</v>
       </c>
       <c r="H112" t="n">
-        <v>3448.6</v>
+        <v>203.13</v>
       </c>
       <c r="I112" t="n">
-        <v>229351.82</v>
+        <v>19908.12</v>
       </c>
       <c r="J112" t="n">
-        <v>125.04</v>
+        <v>98.81</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>great_circle</t>
+          <t>detour_factor</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LN-PNG-HEL-001-AIRFB</t>
+          <t>LN-PNG-WHP-001-ROAD</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -15906,17 +16191,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PNG-HEL-001</t>
+          <t>PNG-WHP-001</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -15925,30 +16210,30 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>294.0252</v>
+        <v>392.0336</v>
       </c>
       <c r="H113" t="n">
-        <v>3542.1</v>
+        <v>141.86</v>
       </c>
       <c r="I113" t="n">
-        <v>1041467.05</v>
+        <v>55613</v>
       </c>
       <c r="J113" t="n">
-        <v>142.69</v>
+        <v>2.42</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>great_circle</t>
+          <t>detour_factor</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LN-PNG-HEL-002-AIRFB</t>
+          <t>LN-PNG-WHP-002-ROAD</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -15958,17 +16243,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PNG-HEL-002</t>
+          <t>PNG-WHP-002</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -15977,30 +16262,30 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>150.5129</v>
+        <v>119.0102</v>
       </c>
       <c r="H114" t="n">
-        <v>3542.1</v>
+        <v>178.01</v>
       </c>
       <c r="I114" t="n">
-        <v>533131.9399999999</v>
+        <v>21185.13</v>
       </c>
       <c r="J114" t="n">
-        <v>167.72</v>
+        <v>56.51</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>great_circle</t>
+          <t>detour_factor</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LN-PNG-ENG-003-AIRFB</t>
+          <t>LN-PNG-WHP-003-ROAD</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -16010,17 +16295,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PNG-ENG-003</t>
+          <t>PNG-WHP-003</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -16029,30 +16314,30 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>133.0114</v>
+        <v>108.5093</v>
       </c>
       <c r="H115" t="n">
-        <v>3542.1</v>
+        <v>182.48</v>
       </c>
       <c r="I115" t="n">
-        <v>471139.86</v>
+        <v>19800.99</v>
       </c>
       <c r="J115" t="n">
-        <v>95.01000000000001</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>great_circle</t>
+          <t>detour_factor</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LN-PNG-SHP-005-AIRFB</t>
+          <t>LN-PNG-WHP-004-ROAD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -16062,17 +16347,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PNG-SHP-005</t>
+          <t>PNG-WHP-004</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Wet season air charter</t>
+          <t>Mount Hagen Area Medical Store road distribution</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -16081,24 +16366,1012 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>80.5069</v>
+        <v>77.00660000000001</v>
       </c>
       <c r="H116" t="n">
-        <v>3542.1</v>
+        <v>165.45</v>
       </c>
       <c r="I116" t="n">
-        <v>285163.6</v>
+        <v>12740.99</v>
       </c>
       <c r="J116" t="n">
-        <v>91.47</v>
+        <v>35.36</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>great_circle</t>
+          <t>detour_factor</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>LN-PNG-WHP-005-ROAD</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>AMS-HGN</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PNG-WHP-005</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>91.0078</v>
+      </c>
+      <c r="H117" t="n">
+        <v>156.29</v>
+      </c>
+      <c r="I117" t="n">
+        <v>14223.38</v>
+      </c>
+      <c r="J117" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>LN-PNG-JIW-001-ROAD</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>AMS-HGN</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>PNG-JIW-001</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>203.0174</v>
+      </c>
+      <c r="H118" t="n">
+        <v>183.23</v>
+      </c>
+      <c r="I118" t="n">
+        <v>37199.41</v>
+      </c>
+      <c r="J118" t="n">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>LN-PNG-JIW-002-ROAD</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>AMS-HGN</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PNG-JIW-002</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>143.5123</v>
+      </c>
+      <c r="H119" t="n">
+        <v>178.57</v>
+      </c>
+      <c r="I119" t="n">
+        <v>25626.63</v>
+      </c>
+      <c r="J119" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>LN-PNG-JIW-003-ROAD</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>AMS-HGN</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PNG-JIW-003</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>164.5141</v>
+      </c>
+      <c r="H120" t="n">
+        <v>175.03</v>
+      </c>
+      <c r="I120" t="n">
+        <v>28794.64</v>
+      </c>
+      <c r="J120" t="n">
+        <v>66.53</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>LN-PNG-JIW-004-ROAD</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>AMS-HGN</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PNG-JIW-004</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>84.0072</v>
+      </c>
+      <c r="H121" t="n">
+        <v>203.11</v>
+      </c>
+      <c r="I121" t="n">
+        <v>17062.61</v>
+      </c>
+      <c r="J121" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>LN-PNG-CHM-001-ROAD</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>AMS-HGN</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PNG-CHM-001</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>259.0222</v>
+      </c>
+      <c r="H122" t="n">
+        <v>214.14</v>
+      </c>
+      <c r="I122" t="n">
+        <v>55468.09</v>
+      </c>
+      <c r="J122" t="n">
+        <v>144.34</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>LN-PNG-CHM-002-ROAD</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>AMS-HGN</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PNG-CHM-002</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>161.0138</v>
+      </c>
+      <c r="H123" t="n">
+        <v>197.61</v>
+      </c>
+      <c r="I123" t="n">
+        <v>31817.95</v>
+      </c>
+      <c r="J123" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>LN-PNG-CHM-003-ROAD</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>AMS-HGN</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PNG-CHM-003</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>115.5099</v>
+      </c>
+      <c r="H124" t="n">
+        <v>225.24</v>
+      </c>
+      <c r="I124" t="n">
+        <v>26017.89</v>
+      </c>
+      <c r="J124" t="n">
+        <v>136.06</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>LN-PNG-CHM-005-ROAD</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>AMS-HGN</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PNG-CHM-005</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>101.5087</v>
+      </c>
+      <c r="H125" t="n">
+        <v>231.27</v>
+      </c>
+      <c r="I125" t="n">
+        <v>23475.55</v>
+      </c>
+      <c r="J125" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>LN-PNG-CHM-006-ROAD</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>AMS-HGN</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PNG-CHM-006</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Mount Hagen Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>87.50749999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>235.64</v>
+      </c>
+      <c r="I126" t="n">
+        <v>20620.3</v>
+      </c>
+      <c r="J126" t="n">
+        <v>153.57</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>LN-PNG-EHP-001-ROAD</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>AMS-LAE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PNG-EHP-001</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Lae Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>378.0324</v>
+      </c>
+      <c r="H127" t="n">
+        <v>274.06</v>
+      </c>
+      <c r="I127" t="n">
+        <v>103603.85</v>
+      </c>
+      <c r="J127" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>LN-PNG-EHP-002-ROAD</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>AMS-LAE</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PNG-EHP-002</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Lae Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>217.0186</v>
+      </c>
+      <c r="H128" t="n">
+        <v>223.15</v>
+      </c>
+      <c r="I128" t="n">
+        <v>48426.94</v>
+      </c>
+      <c r="J128" t="n">
+        <v>233.57</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>LN-PNG-EHP-003-ROAD</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>AMS-LAE</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PNG-EHP-003</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Lae Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>119.0102</v>
+      </c>
+      <c r="H129" t="n">
+        <v>276.18</v>
+      </c>
+      <c r="I129" t="n">
+        <v>32868.7</v>
+      </c>
+      <c r="J129" t="n">
+        <v>282.24</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>LN-PNG-EHP-004-ROAD</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>AMS-LAE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PNG-EHP-004</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Lae Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>108.5093</v>
+      </c>
+      <c r="H130" t="n">
+        <v>319.43</v>
+      </c>
+      <c r="I130" t="n">
+        <v>34660.77</v>
+      </c>
+      <c r="J130" t="n">
+        <v>355.07</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>LN-PNG-EHP-005-ROAD</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>AMS-LAE</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>PNG-EHP-005</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Lae Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>98.00839999999999</v>
+      </c>
+      <c r="H131" t="n">
+        <v>279.13</v>
+      </c>
+      <c r="I131" t="n">
+        <v>27357.56</v>
+      </c>
+      <c r="J131" t="n">
+        <v>287.21</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>LN-PNG-ENB-001-ROAD</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>AMS-KOK</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PNG-ENB-001</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Kokopo Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>322.0276</v>
+      </c>
+      <c r="H132" t="n">
+        <v>186.13</v>
+      </c>
+      <c r="I132" t="n">
+        <v>59940.31</v>
+      </c>
+      <c r="J132" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>LN-PNG-ENB-002-ROAD</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>AMS-KOK</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PNG-ENB-002</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Kokopo Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>213.5183</v>
+      </c>
+      <c r="H133" t="n">
+        <v>168.32</v>
+      </c>
+      <c r="I133" t="n">
+        <v>35938.8</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>LN-PNG-ENB-003-ROAD</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>AMS-KOK</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>PNG-ENB-003</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Kokopo Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>133.0114</v>
+      </c>
+      <c r="H134" t="n">
+        <v>188.79</v>
+      </c>
+      <c r="I134" t="n">
+        <v>25110.71</v>
+      </c>
+      <c r="J134" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>LN-PNG-ENB-004-ROAD</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>AMS-KOK</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PNG-ENB-004</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Kokopo Area Medical Store road distribution</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>73.5063</v>
+      </c>
+      <c r="H135" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="I135" t="n">
+        <v>13232.87</v>
+      </c>
+      <c r="J135" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>detour_factor</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -16201,19 +17474,19 @@
         <v>1034000</v>
       </c>
       <c r="D5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="E5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>3098606.05</v>
+        <v>1527154.62</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1.48</v>
       </c>
       <c r="I5" t="n">
         <v>0.0537</v>
@@ -16241,10 +17514,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>4537731.81</v>
+        <v>1692101.12</v>
       </c>
       <c r="H6" t="n">
-        <v>4.91</v>
+        <v>1.83</v>
       </c>
       <c r="I6" t="n">
         <v>0.1476</v>
@@ -16266,16 +17539,16 @@
         <v>3486.3</v>
       </c>
       <c r="E7" t="n">
-        <v>2663.7</v>
+        <v>3486.3</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7641</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1568952.25</v>
+        <v>1840614.96</v>
       </c>
       <c r="H7" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="I7" t="n">
         <v>0.2294</v>
@@ -16294,19 +17567,19 @@
         <v>967500</v>
       </c>
       <c r="D8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="E8" t="n">
-        <v>2245.6</v>
+        <v>3386.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6631</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1513553.33</v>
+        <v>2055534.42</v>
       </c>
       <c r="H8" t="n">
-        <v>1.56</v>
+        <v>2.12</v>
       </c>
       <c r="I8" t="n">
         <v>0.3065</v>
@@ -16328,16 +17601,16 @@
         <v>3407.5</v>
       </c>
       <c r="E9" t="n">
-        <v>3299</v>
+        <v>3407.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9681999999999999</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>4550305.44</v>
+        <v>4128773.37</v>
       </c>
       <c r="H9" t="n">
-        <v>4.67</v>
+        <v>4.24</v>
       </c>
       <c r="I9" t="n">
         <v>0.4332</v>
@@ -16389,7 +17662,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>Annualised</t>
         </is>
       </c>
     </row>
@@ -16425,7 +17698,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -16437,7 +17710,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -16497,7 +17770,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'month': 2, 'allowed_modes': ['road', 'sea', 'air', 'river'], 'hub_nodes_open': [], 'hub_nodes_closed': ['AMS-WWK', 'AMS-ALO', 'AMS-BUK'], 'optimize_hubs': False, 'integration_policy': 'vertical', 'third_party_share': 0, 'fuel_index': 1, 'demand_growth': 0, 'safety_stock_days': 14}</t>
+          <t>{'month': None, 'allowed_modes': ['road', 'sea', 'air', 'river'], 'hub_nodes_open': [], 'hub_nodes_closed': ['AMS-WWK', 'AMS-ALO', 'AMS-BUK'], 'optimize_hubs': False, 'integration_policy': 'vertical', 'third_party_share': 0.0, 'fuel_index': 1.0, 'demand_growth': 0.0, 'safety_stock_days': 14.0}</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 113 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 59 ms</t>
         </is>
       </c>
     </row>
@@ -707,6 +707,157 @@
         <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Share of demand volume that is estimated</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Facilities with estimated demand</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>134</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9460924.939999999</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>12934481.77</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>count</t>
         </is>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 59 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:50 UTC · 43 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:50 UTC · 43 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 43 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 43 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 42 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 42 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:57 UTC · 48 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:57 UTC · 48 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 91 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 91 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 51 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 51 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 53 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 53 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 52 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 52 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 41 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 41 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 42 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 42 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 126 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-1.xlsx
+++ b/docs/app/api/files/results-1.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 126 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:14 UTC · 113 ms</t>
         </is>
       </c>
     </row>
